--- a/final_papers.xlsx
+++ b/final_papers.xlsx
@@ -471,8 +471,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Bridging Traditional Health Information Management And Modern Data Intelligence
-In A Non-Digitalized Tertiary Hospital</t>
+          <t>Bridging Traditional Health Information Management And Modern Data Intelligence In A Non-Digitalized Tertiary Hospital</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -611,8 +610,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Human Eyes And Artificial Minds: Breast Cancer Detection In Mammography — A
-Systematic Review</t>
+          <t>Human Eyes And Artificial Minds: Breast Cancer Detection In Mammography — A Systematic Review</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -728,8 +726,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Traceable And Reproducible 3D Magnetic Field Mapping For Data-Driven Magnetic
-Drug Targeting</t>
+          <t>Traceable And Reproducible 3D Magnetic Field Mapping For Data-Driven Magnetic Drug Targeting</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -769,8 +766,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Automated Video-Based Surrogate Dose Estimation For Patient-Specific Magnetic
-Drug Targeting Using Time-Resolved Deposition Analysis</t>
+          <t>Automated Video-Based Surrogate Dose Estimation For Patient-Specific Magnetic Drug Targeting Using Time-Resolved Deposition Analysis</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -810,8 +806,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Biomarker-Led Predictive Modelling And Risk Classification In Personalized
-Medicine</t>
+          <t>Biomarker-Led Predictive Modelling And Risk Classification In Personalized Medicine</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -974,8 +969,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Assessing The Impact Of Artificial Intelligence On Medical Equipment And
-Healthcare Technology Management</t>
+          <t>Assessing The Impact Of Artificial Intelligence On Medical Equipment And Healthcare Technology Management</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1011,8 +1005,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Spatial And Temporal Patterns In Type 2 Diabetes Dynamics In Romania – A 10-Year
-Time Series Study</t>
+          <t>Spatial And Temporal Patterns In Type 2 Diabetes Dynamics In Romania – A 10-Year Time Series Study</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1050,8 +1043,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Laboratory Informatics Artificial Intelligence-Based Quality Control: Reagent
-Validation Models, Drift Detection And Nonconformance Prevention In Transfusion Tests.</t>
+          <t>Laboratory Informatics Artificial Intelligence-Based Quality Control: Reagent Validation Models, Drift Detection And Nonconformance Prevention In Transfusion Tests.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1086,8 +1078,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>The Opinion Of The General Romanian Population On Introducing An Ai-Powered
-Medical Data Collector</t>
+          <t>The Opinion Of The General Romanian Population On Introducing An Ai-Powered Medical Data Collector</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1163,8 +1154,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>A Frequency-Based Electroencephalography Approach To Real-Time Attention
-Detection</t>
+          <t>A Frequency-Based Electroencephalography Approach To Real-Time Attention Detection</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1202,8 +1192,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>A Comparative Analysis Of The Performance Of Machine Learning Models In Fair
-Health Data From Uganda, Africa</t>
+          <t>A Comparative Analysis Of The Performance Of Machine Learning Models In Fair Health Data From Uganda, Africa</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1242,8 +1231,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Automated Detection Of Coronary Artery Disease From Multiparametric Cardiac
-Magnetic Resonance Imaging Using Deep Learning</t>
+          <t>Automated Detection Of Coronary Artery Disease From Multiparametric Cardiac Magnetic Resonance Imaging Using Deep Learning</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1282,8 +1270,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Measles Outbreak Prediction Using Machine Learning Models: A Regional
-Surveillance Study From South-West Romania</t>
+          <t>Measles Outbreak Prediction Using Machine Learning Models: A Regional Surveillance Study From South-West Romania</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1323,8 +1310,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Artificial Intelligence For Polysomnographic Analysis: Clinical Validation,
-Technical Architecture And Real-World Implementation Of Somnolyzer</t>
+          <t>Artificial Intelligence For Polysomnographic Analysis: Clinical Validation, Technical Architecture And Real-World Implementation Of Somnolyzer</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1363,8 +1349,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Perception And Level Of Acceptance Of The General Population In Romania
-Regarding The Use Of Wearable Devices For Health Monitoring</t>
+          <t>Perception And Level Of Acceptance Of The General Population In Romania Regarding The Use Of Wearable Devices For Health Monitoring</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1483,8 +1468,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Trustworthy Transformer Models For Thyroid Cancer Recurrence Prediction Through
-Explanation Stability</t>
+          <t>Trustworthy Transformer Models For Thyroid Cancer Recurrence Prediction Through Explanation Stability</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1524,8 +1508,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Physics-Informed Neural Networks For Robust Multiple Sclerosis Lesion Detection:
-Integrating Bloch-Based Pre-Training</t>
+          <t>Physics-Informed Neural Networks For Robust Multiple Sclerosis Lesion Detection: Integrating Bloch-Based Pre-Training</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1603,8 +1586,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Automated Breast Lesion Segmentation In Ultrasound Images Using Attention U-Net
-Architectures</t>
+          <t>Automated Breast Lesion Segmentation In Ultrasound Images Using Attention U-Net Architectures</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1680,8 +1662,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Pharmacological Space Mapping Via Structure-Target Relationship Using Layered
-Soms</t>
+          <t>Pharmacological Space Mapping Via Structure-Target Relationship Using Layered Soms</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1722,8 +1703,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Real-Time Sleep Stage Monitoring Using Neural Networks For Optimal Wake-Up
-Timing</t>
+          <t>Real-Time Sleep Stage Monitoring Using Neural Networks For Optimal Wake-Up Timing</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
